--- a/projects/particle-tracking-study/Partical track study.xlsx
+++ b/projects/particle-tracking-study/Partical track study.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epropelledsys-my.sharepoint.com/personal/ankitg_epropelled_com/Documents/Study/heatlight particle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="11_F25DC773A252ABDACC104855519B48485BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{073DD36B-53A3-4083-8D61-DF6BED05E80C}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="11_F25DC773A252ABDACC104855519B48485BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D64A3B64-3E24-4473-B6AB-9CF154979F86}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-8895" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-8895" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="1" r:id="rId1"/>
@@ -534,23 +534,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>201167</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>105428</xdr:rowOff>
+      <xdr:colOff>153539</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>86374</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42F27A08-6375-3ECA-9DEB-F758F86F52DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10114F30-FF5B-7C9C-8C18-7673999302AD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -566,8 +566,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1219200" y="2857500"/>
-          <a:ext cx="8183117" cy="4677428"/>
+          <a:off x="1190625" y="2676525"/>
+          <a:ext cx="8164064" cy="4648849"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -578,23 +578,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>201167</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>105428</xdr:rowOff>
+      <xdr:colOff>267855</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>57795</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="8" name="Picture 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F866B20-92AA-439F-7D68-A9CDC421125A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76B9EA4F-D37F-8519-0D51-BEEC38A66D7A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -603,15 +603,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1219200" y="8001000"/>
-          <a:ext cx="8183117" cy="4677428"/>
+          <a:off x="1190625" y="7629525"/>
+          <a:ext cx="8278380" cy="4620270"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -622,23 +622,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>201167</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>105428</xdr:rowOff>
+      <xdr:colOff>86855</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>57795</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="9" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66E166B2-5E7D-30EC-9B47-84DF834B7EAF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31ECD9AC-0ECE-7A37-58AF-6E7078EDDDE6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -647,15 +647,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1219200" y="12954000"/>
-          <a:ext cx="8183117" cy="4677428"/>
+          <a:off x="1190625" y="12582525"/>
+          <a:ext cx="8097380" cy="4620270"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -666,23 +666,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>201167</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>105428</xdr:rowOff>
+      <xdr:colOff>305961</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>95900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
+        <xdr:cNvPr id="10" name="Picture 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BC598E6-1B0C-B5E4-E9B6-437595ADAF91}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24DF1EA1-5187-0A1B-4930-51B24C1AC1AA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -691,15 +691,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1219200" y="17907000"/>
-          <a:ext cx="8183117" cy="4677428"/>
+          <a:off x="1190625" y="17535525"/>
+          <a:ext cx="8316486" cy="4658375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -710,23 +710,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>201167</xdr:colOff>
-      <xdr:row>144</xdr:row>
-      <xdr:rowOff>105428</xdr:rowOff>
+      <xdr:colOff>172592</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>124479</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="11" name="Picture 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55DCA8D9-042D-E0FC-E517-A84EE3A0B3AF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B5A11D9-026A-4BC3-2CC9-C60B7BCCCC5D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -735,15 +735,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1219200" y="22860000"/>
-          <a:ext cx="8183117" cy="4677428"/>
+          <a:off x="1190625" y="22488525"/>
+          <a:ext cx="8183117" cy="4686954"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/projects/particle-tracking-study/Partical track study.xlsx
+++ b/projects/particle-tracking-study/Partical track study.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epropelledsys-my.sharepoint.com/personal/ankitg_epropelled_com/Documents/Study/heatlight particle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="11_F25DC773A252ABDACC104855519B48485BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D64A3B64-3E24-4473-B6AB-9CF154979F86}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="11_F25DC773A252ABDACC104855519B48485BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF3A18B1-62B8-40D9-8D47-9FA5BC6906A9}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-8895" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="1" r:id="rId1"/>
     <sheet name="Steady-flow" sheetId="2" r:id="rId2"/>
     <sheet name="trans error" sheetId="3" r:id="rId3"/>
     <sheet name="trans_Idealgas" sheetId="4" r:id="rId4"/>
+    <sheet name="trans ts 1s" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="23">
   <si>
     <t>Steady</t>
   </si>
@@ -744,6 +745,803 @@
         <a:xfrm>
           <a:off x="1190625" y="22488525"/>
           <a:ext cx="8183117" cy="4686954"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE7896A7-0E94-B3E5-E9B9-4B739FF67671}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="2476500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8773BCE0-9A43-ACC3-EADC-43DF08D83626}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="8572500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{852013D4-CA1F-DAF9-FA6E-95992E304063}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="14668500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD43D1C9-69E0-206A-BD36-D5B87EBC4F37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="20764500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF9029AB-E42C-0864-E5BB-99F3A5F05554}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="26860500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06431F4E-479C-4D67-CA4E-8FBFC3E5BCCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="33147000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81C4FB93-DFCF-699B-61AF-53B794F63263}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11582400" y="2286000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13B9D4E7-62C9-36FE-2689-28C140A1DF60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11582400" y="8572500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93FB7EB8-4943-1A85-40B8-65312C029E1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11582400" y="14668500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{049127DE-10B0-B900-61BB-728101E98E1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11582400" y="20764500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59DB27E8-D7B6-55B9-6881-0AFF0D7B5985}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11582400" y="26860500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8309B310-8D3F-4D1C-8261-BD0CFAEFCD6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11582400" y="33147000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E38B6C2C-1A00-000E-15A2-57159117E24D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21945600" y="2286000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F035317-3987-DAF1-99A5-D201E5F51FB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21945600" y="8382000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7527595-4E08-BDAB-8E39-5A55BF76B50C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21945600" y="14478000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D9FE303-5736-16A8-3C97-AD7255EB6302}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21945600" y="20764500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F0D532E-F8A6-433F-6416-FDB99CB87531}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21945600" y="26860500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82D19775-B470-4B32-931B-7121FF20B443}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21945600" y="33147000"/>
+          <a:ext cx="9504762" cy="5904762"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1325,4 +2123,92 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0811C199-F276-43BD-9E33-7ED793022DBD}">
+  <dimension ref="C3:G11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>-2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>0.1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/projects/particle-tracking-study/Partical track study.xlsx
+++ b/projects/particle-tracking-study/Partical track study.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epropelledsys-my.sharepoint.com/personal/ankitg_epropelled_com/Documents/Study/heatlight particle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="11_F25DC773A252ABDACC104855519B48485BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF3A18B1-62B8-40D9-8D47-9FA5BC6906A9}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="11_F25DC773A252ABDACC104855519B48485BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB8D5080-CDC1-43E9-B8A0-A70C71E36427}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="1" r:id="rId1"/>
     <sheet name="Steady-flow" sheetId="2" r:id="rId2"/>
     <sheet name="trans error" sheetId="3" r:id="rId3"/>
-    <sheet name="trans_Idealgas" sheetId="4" r:id="rId4"/>
+    <sheet name="trans_Idealgas ts 0p1s" sheetId="4" r:id="rId4"/>
     <sheet name="trans ts 1s" sheetId="5" r:id="rId5"/>
+    <sheet name="trans ts 0p01s" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="23">
   <si>
     <t>Steady</t>
   </si>
@@ -1542,6 +1543,319 @@
         <a:xfrm>
           <a:off x="21945600" y="33147000"/>
           <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FACA98E5-37F3-91BB-417F-2B9F1FA3EF6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="2476500"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{202DD7E2-AB21-393D-65E4-AE44DC60CA25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="8763000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E87EA6B6-B661-47F5-FBCB-FF7102D8FD97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="15240000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2FEF02E-BEF0-B38E-740A-4FFDF6397AFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="21717000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9781E4C2-840E-C580-542C-9DCDFD1457B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="28194000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>360762</xdr:colOff>
+      <xdr:row>216</xdr:row>
+      <xdr:rowOff>189762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFAA24D2-EC05-9C31-C3B1-802DB26F6367}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="35433000"/>
+          <a:ext cx="9504762" cy="5904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>505406</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>181798</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47246D03-8172-9517-A9EA-2B78CDE3214B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11582400" y="1143000"/>
+          <a:ext cx="4163006" cy="5896798"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2211,4 +2525,92 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995760A7-EC22-41F5-904D-495EF359B99D}">
+  <dimension ref="C3:G11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>-2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>0.1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>0.01</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>